--- a/output/laminas_comunales/comunal_i_ingr_mean_a_2020_coquimbo.xlsx
+++ b/output/laminas_comunales/comunal_i_ingr_mean_a_2020_coquimbo.xlsx
@@ -674,7 +674,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:A16"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -683,11 +683,6 @@
           <t>Comuna</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>2020</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -695,138 +690,103 @@
           <t>Andacollo</t>
         </is>
       </c>
-      <c r="B2">
-        <v>280187</v>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Canela</t>
-        </is>
-      </c>
-      <c r="B3">
-        <v>159266.69</v>
+          <t>Los Vilos</t>
+        </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Combarbalá</t>
-        </is>
-      </c>
-      <c r="B4">
-        <v>193057.61</v>
+          <t>Canela</t>
+        </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
-        </is>
-      </c>
-      <c r="B5">
-        <v>289912.75</v>
+          <t>Ovalle</t>
+        </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Illapel</t>
-        </is>
-      </c>
-      <c r="B6">
-        <v>277309.22</v>
+          <t>Coquimbo</t>
+        </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>La Higuera</t>
-        </is>
-      </c>
-      <c r="B7">
-        <v>163624.78</v>
+          <t>La Serena</t>
+        </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>La Serena</t>
-        </is>
-      </c>
-      <c r="B8">
-        <v>338940.31</v>
+          <t>Combarbalá</t>
+        </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Los Vilos</t>
-        </is>
-      </c>
-      <c r="B9">
-        <v>193369.5</v>
+          <t>Punitaqui</t>
+        </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Monte Patria</t>
-        </is>
-      </c>
-      <c r="B10">
-        <v>201652.36</v>
+          <t>Paihuano</t>
+        </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Ovalle</t>
-        </is>
-      </c>
-      <c r="B11">
-        <v>247571.48</v>
+          <t>Illapel</t>
+        </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Punitaqui</t>
-        </is>
-      </c>
-      <c r="B12">
-        <v>218021.75</v>
+          <t>La Higuera</t>
+        </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Río Hurtado</t>
-        </is>
-      </c>
-      <c r="B13">
-        <v>192886.88</v>
+          <t>Monte Patria</t>
+        </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Salamanca</t>
-        </is>
-      </c>
-      <c r="B14">
-        <v>286244.97</v>
+          <t>Río Hurtado</t>
+        </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
+          <t>Salamanca</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
           <t>Vicuña</t>
         </is>
-      </c>
-      <c r="B15">
-        <v>226179.64</v>
       </c>
     </row>
   </sheetData>
